--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487498_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487498_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4148</v>
+        <v>0.5068</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6437</v>
+        <v>1.7625</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.229</v>
+        <v>-1.2557</v>
       </c>
       <c r="G2" t="n">
         <v>2.0793</v>
@@ -610,13 +610,13 @@
         <v>0.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2313</v>
+        <v>-0.1392</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.297</v>
+        <v>-0.1782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8815</v>
+        <v>-0.8327</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7398</v>
+        <v>-0.6375</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1417</v>
+        <v>-0.1952</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7512</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1303</v>
+        <v>-0.0815</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0115</v>
+        <v>-0.065</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3542</v>
+        <v>-2.3981</v>
       </c>
       <c r="E4" t="n">
-        <v>2.177</v>
+        <v>1.5049</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.5313</v>
+        <v>-3.903</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9076</v>
+        <v>-0.0196</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3826</v>
+        <v>2.0771</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.525</v>
+        <v>-2.0968</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1193</v>
+        <v>2.9334</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6755</v>
+        <v>4.9301</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5562</v>
+        <v>-1.9967</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.027</v>
+        <v>-2.953</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.0581</v>
+        <v>-2.8529</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0311</v>
+        <v>-0.1001</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7626</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2573</v>
+        <v>-0.7702</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4447</v>
+        <v>0.2547</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1874</v>
+        <v>-1.0248</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9412</v>
+        <v>-1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5507</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
         <v>-1.492</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.9459</v>
+        <v>-3.338</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2244</v>
+        <v>-0.2006</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.1703</v>
+        <v>-3.1374</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0196</v>
+        <v>-2.6736</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0771</v>
+        <v>-2.654</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0968</v>
+        <v>-0.0197</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9334</v>
+        <v>-0.0539</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9301</v>
+        <v>-0.1396</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9967</v>
+        <v>0.0857</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.953</v>
+        <v>-2.6197</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.8529</v>
+        <v>-2.5144</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1001</v>
+        <v>-0.1053</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.318</v>
+        <v>-0.6068</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0259</v>
+        <v>-0.3264</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2921</v>
+        <v>-0.2804</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="X5" t="n">
         <v>-1.2166</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.3661</v>
+        <v>-3.5692</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3623</v>
+        <v>-0.9529</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0038</v>
+        <v>-2.6163</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6736</v>
+        <v>-2.5183</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.654</v>
+        <v>-3.0589</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0197</v>
+        <v>0.5406</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0539</v>
+        <v>0.9107</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1396</v>
+        <v>0.4064</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0857</v>
+        <v>0.5043</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6197</v>
+        <v>-3.429</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5144</v>
+        <v>-3.4654</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1053</v>
+        <v>0.0363</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6349</v>
+        <v>-1.3517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4882</v>
+        <v>-0.2647</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1467</v>
+        <v>-1.087</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0576</v>
+        <v>2.651</v>
       </c>
       <c r="W6" t="n">
-        <v>1.159</v>
+        <v>2.318</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2166</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.2056</v>
+        <v>-4.1194</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8976</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.308</v>
+        <v>-3.2813</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1401</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4156</v>
+        <v>-0.3295</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.297</v>
+        <v>-0.2376</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V7" t="n">
         <v>-3.0415</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.0068</v>
+        <v>-4.2423</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2568</v>
+        <v>-0.2032</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.75</v>
+        <v>-4.0391</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5183</v>
+        <v>-1.9076</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0589</v>
+        <v>-1.3826</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5406</v>
+        <v>-0.525</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9107</v>
+        <v>1.1193</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4064</v>
+        <v>1.6755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5043</v>
+        <v>-0.5562</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.429</v>
+        <v>-3.027</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.4654</v>
+        <v>-3.0581</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0363</v>
+        <v>0.0311</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3502</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.7892</v>
+        <v>0.3692</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5686</v>
+        <v>1.0645</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2207</v>
+        <v>-0.6953</v>
       </c>
       <c r="V8" t="n">
-        <v>2.651</v>
+        <v>-0.9412</v>
       </c>
       <c r="W8" t="n">
-        <v>2.318</v>
+        <v>0.5507</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3329</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.7151</v>
+        <v>-5.7569</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3984</v>
+        <v>-2.5203</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3167</v>
+        <v>-3.2365</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4215</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9227</v>
+        <v>-0.9644</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8557</v>
+        <v>0.0223</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0669</v>
+        <v>-0.9867</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.3689</v>
+        <v>-7.7886</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8431</v>
+        <v>-2.4767</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5258</v>
+        <v>-5.312</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5215</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2172</v>
+        <v>-0.637</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1317</v>
+        <v>0.2347</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0855</v>
+        <v>-0.8716</v>
       </c>
       <c r="V10" t="n">
         <v>-2.651</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-32.4293</v>
+        <v>-31.5384</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.452900000000001</v>
+        <v>-4.561999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-26.9766</v>
+        <v>-26.97650000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-11.8741</v>
@@ -1291,7 +1291,7 @@
         <v>7.447300000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.176400000000001</v>
+        <v>-2.1764</v>
       </c>
       <c r="M11" t="n">
         <v>-17.1452</v>
@@ -1309,13 +1309,13 @@
         <v>-14.6886</v>
       </c>
       <c r="R11" t="n">
-        <v>7.8339</v>
+        <v>7.833899999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.401899999999999</v>
+        <v>-4.511100000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3382000000000002</v>
+        <v>0.5528</v>
       </c>
       <c r="U11" t="n">
         <v>-5.0637</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.2633</v>
+        <v>8.7578</v>
       </c>
       <c r="E12" t="n">
-        <v>9.3484</v>
+        <v>7.8133</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9149</v>
+        <v>0.9445</v>
       </c>
       <c r="G12" t="n">
         <v>4.697</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5871</v>
+        <v>1.0816</v>
       </c>
       <c r="T12" t="n">
-        <v>2.716</v>
+        <v>1.181</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1289</v>
+        <v>-0.0994</v>
       </c>
       <c r="V12" t="n">
         <v>1.2166</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6501</v>
+        <v>5.8077</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8989</v>
+        <v>5.0671</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7512</v>
+        <v>0.7406</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4019</v>
+        <v>4.5576</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4927</v>
+        <v>3.5724</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9092</v>
+        <v>0.9852</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5842</v>
+        <v>4.7389</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9635</v>
+        <v>4.0422</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6207</v>
+        <v>0.6967</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1823</v>
+        <v>-0.1813</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4708</v>
+        <v>-0.4698</v>
       </c>
       <c r="O13" t="n">
         <v>0.2885</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7181999999999999</v>
+        <v>-0.2372</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3515</v>
+        <v>0.3282</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6333</v>
+        <v>-0.5653</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0576</v>
+        <v>-0.2754</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5353</v>
+        <v>5.0783</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3793</v>
+        <v>3.7886</v>
       </c>
       <c r="F14" t="n">
-        <v>1.156</v>
+        <v>1.2897</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1058</v>
@@ -1546,13 +1546,13 @@
         <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2079</v>
+        <v>0.7509</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2376</v>
+        <v>0.1717</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4455</v>
+        <v>0.5792</v>
       </c>
       <c r="V14" t="n">
         <v>3.6498</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3004</v>
+        <v>4.1486</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0437</v>
+        <v>3.2849</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2567</v>
+        <v>0.8637</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5576</v>
+        <v>3.4019</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5724</v>
+        <v>2.4927</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9852</v>
+        <v>0.9092</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7389</v>
+        <v>3.5842</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0422</v>
+        <v>2.9635</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6967</v>
+        <v>0.6207</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1813</v>
+        <v>-0.1823</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4698</v>
+        <v>-0.4708</v>
       </c>
       <c r="O15" t="n">
         <v>0.2885</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7445</v>
+        <v>0.2167</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6952</v>
+        <v>0.7375</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0493</v>
+        <v>-0.5208</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2754</v>
+        <v>-0.0576</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.451</v>
+        <v>3.1081</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3585</v>
+        <v>3.2562</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0925</v>
+        <v>-0.1481</v>
       </c>
       <c r="G16" t="n">
         <v>1.7628</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4129</v>
+        <v>1.07</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9487</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4642</v>
+        <v>0.2236</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3881</v>
+        <v>2.7071</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6389</v>
+        <v>3.7413</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2508</v>
+        <v>-1.0342</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2558</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3858</v>
+        <v>0.7047</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0288</v>
+        <v>0.1312</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3569</v>
+        <v>0.5736</v>
       </c>
       <c r="V17" t="n">
         <v>3.0415</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9325</v>
+        <v>1.9194</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1153</v>
+        <v>1.1073</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0477</v>
+        <v>0.8121</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4491</v>
+        <v>0.4981</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2483</v>
+        <v>0.6145</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6974</v>
+        <v>-0.1164</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2123</v>
+        <v>1.095</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9254</v>
+        <v>1.7676</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.713</v>
+        <v>-0.6726</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6615</v>
+        <v>-0.5969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.677</v>
+        <v>-1.153</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0156</v>
+        <v>0.5562</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1489</v>
+        <v>-0.0072</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8475</v>
+        <v>0.0123</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3014</v>
+        <v>-0.0196</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5507</v>
+        <v>0.0576</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5507</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5175</v>
+        <v>1.5924</v>
       </c>
       <c r="E19" t="n">
-        <v>1.005</v>
+        <v>-0.2176</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5125</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4981</v>
+        <v>-0.4491</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6145</v>
+        <v>0.2483</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1164</v>
+        <v>-0.6974</v>
       </c>
       <c r="J19" t="n">
-        <v>1.095</v>
+        <v>0.2123</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7676</v>
+        <v>0.9254</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6726</v>
+        <v>-0.713</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5969</v>
+        <v>-0.6615</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.153</v>
+        <v>-0.677</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5562</v>
+        <v>0.0156</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4092</v>
+        <v>1.8088</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.09</v>
+        <v>0.7452</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3192</v>
+        <v>1.0636</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0576</v>
+        <v>-0.5507</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0576</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2097</v>
+        <v>1.0926</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1733</v>
+        <v>-0.4803</v>
       </c>
       <c r="F20" t="n">
-        <v>1.383</v>
+        <v>1.5729</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9408</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4419</v>
+        <v>1.3248</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8299</v>
+        <v>0.5228</v>
       </c>
       <c r="U20" t="n">
-        <v>0.612</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.492</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SOTO MARTINEZ</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8903</v>
+        <v>-0.1463</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6196</v>
+        <v>-0.2763</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2707</v>
+        <v>0.13</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2175</v>
+        <v>-1.0741</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8037</v>
+        <v>-0.2858</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5862000000000001</v>
+        <v>-0.7883</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5602</v>
+        <v>-0.2116</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6006</v>
+        <v>-0.2212</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0404</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3427</v>
+        <v>-0.8625</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2031</v>
+        <v>-0.0646</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5458</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3975</v>
+        <v>-0.1678</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0594</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3381</v>
+        <v>-0.1031</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>A. SOTO MARTINEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.928</v>
+        <v>-0.2717</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.788</v>
+        <v>-0.1079</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1401</v>
+        <v>-0.1638</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0741</v>
+        <v>-0.2175</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2858</v>
+        <v>-0.8037</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7883</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2116</v>
+        <v>-0.5602</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2212</v>
+        <v>-0.6006</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8625</v>
+        <v>0.3427</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0646</v>
+        <v>-0.2031</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.5458</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9495</v>
+        <v>0.2211</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5764</v>
+        <v>0.4523</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3732</v>
+        <v>-0.2311</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>32.4296</v>
+        <v>33.794</v>
       </c>
       <c r="E23" t="n">
-        <v>26.9765</v>
+        <v>26.9766</v>
       </c>
       <c r="F23" t="n">
-        <v>5.452900000000001</v>
+        <v>6.817399999999999</v>
       </c>
       <c r="G23" t="n">
         <v>11.8743</v>
@@ -2227,7 +2227,7 @@
         <v>17.3269</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1817999999999998</v>
+        <v>-0.1818000000000002</v>
       </c>
       <c r="M23" t="n">
         <v>-5.270899999999999</v>
@@ -2248,13 +2248,13 @@
         <v>14.6884</v>
       </c>
       <c r="S23" t="n">
-        <v>5.402000000000001</v>
+        <v>6.766399999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>5.063800000000001</v>
+        <v>5.0638</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3380000000000001</v>
+        <v>1.7026</v>
       </c>
       <c r="V23" t="n">
         <v>8.298400000000001</v>
